--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/DELAWARE_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/DELAWARE_2011.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C168">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C268">
